--- a/docs/GroupMj Product-Backlog.xlsx
+++ b/docs/GroupMj Product-Backlog.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17260"/>
+    <workbookView windowWidth="32740" windowHeight="16140"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="404">
   <si>
     <t>ID</t>
   </si>
@@ -40,10 +40,10 @@
     <t>Epic</t>
   </si>
   <si>
-    <t>Backlog 项</t>
-  </si>
-  <si>
-    <t>优先级</t>
+    <t>Backlog Item</t>
+  </si>
+  <si>
+    <t>Priority</t>
   </si>
   <si>
     <t>SP</t>
@@ -55,36 +55,34 @@
     <t>Second</t>
   </si>
   <si>
-    <t>验收条件</t>
-  </si>
-  <si>
-    <t>依赖</t>
+    <t>Acceptance Criteria</t>
+  </si>
+  <si>
+    <t>Dependency</t>
   </si>
   <si>
     <t>Sprint</t>
   </si>
   <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>关联需求</t>
-  </si>
-  <si>
-    <t>证据要求</t>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Linked Requirement</t>
+  </si>
+  <si>
+    <t>Evidence Required</t>
   </si>
   <si>
     <t>Mj01</t>
   </si>
   <si>
-    <t>Project Management
-项目管理</t>
-  </si>
-  <si>
-    <t>Confirm the four-person group
-确认 4 人小组</t>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>Confirm the four-person group</t>
   </si>
   <si>
     <t>P0</t>
@@ -96,8 +94,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Approval from the tutor is recorded in writing and stored in the repository.
-导师的批准有书面记录，并已存入仓库。</t>
+    <t>Approval from the tutor is recorded in writing and stored in the repository.</t>
   </si>
   <si>
     <t>-</t>
@@ -109,156 +106,121 @@
     <t>Done</t>
   </si>
   <si>
-    <t>The brief expects five people. Ask the tutor to approve four, and keep the reply.
-任务书按 5 人小组设计，需要请导师批准我们 4 人成组，并保留回复。</t>
-  </si>
-  <si>
-    <t>Assessment brief, section 1 - group size
-考核规范第 1 节 —— 小组人数</t>
-  </si>
-  <si>
-    <t>Screenshot or email from the tutor, saved in docs/
-导师的邮件或消息截图，存放在 docs/ 下</t>
+    <t>The brief expects five people. Ask the tutor to approve four, and keep the reply.</t>
+  </si>
+  <si>
+    <t>Assessment brief, section 1 - group size</t>
+  </si>
+  <si>
+    <t>Screenshot or email from the tutor, saved in docs/</t>
   </si>
   <si>
     <t>Mj02</t>
   </si>
   <si>
-    <t>Agree scope, stakeholders and assumptions
-确定范围、利益相关者与假设</t>
+    <t>Agree scope, stakeholders and assumptions</t>
   </si>
   <si>
     <t>D</t>
   </si>
   <si>
-    <t>A stakeholder list, a scope boundary and a numbered assumption list are agreed by all four.
-干系人清单、范围边界、编号的假设清单，四名成员都已确认。</t>
-  </si>
-  <si>
-    <t>Read the case study together and agree what we build, who is involved, and what we are guessing.
-一起读完案例，定下我们做什么、涉及哪些人、哪些地方是我们的猜测。</t>
-  </si>
-  <si>
-    <t>Case study, closing paragraph
-案例结尾段</t>
-  </si>
-  <si>
-    <t>docs/case-study-analysis.md committed
-docs/case-study-analysis.md 已提交到仓库</t>
+    <t>A stakeholder list, a scope boundary and a numbered assumption list are agreed by all four.</t>
+  </si>
+  <si>
+    <t>Read the case study together and agree what we build, who is involved, and what we are guessing.</t>
+  </si>
+  <si>
+    <t>Case study, closing paragraph</t>
+  </si>
+  <si>
+    <t>docs/case-study-analysis.md committed</t>
   </si>
   <si>
     <t>Mj03</t>
   </si>
   <si>
-    <t>Product backlog and Definition of Done
-产品待办列表与完成定义</t>
-  </si>
-  <si>
-    <t>Every item has a first owner, a second owner, an estimate, acceptance conditions and a dependency.
-每条待办都有第一负责人、第二负责人、估算、验收条件和依赖关系。</t>
-  </si>
-  <si>
-    <t>Write the full list of work, and agree what 'finished' means on this project.
-写出全部工作清单，并商定这个项目里'做完'的标准是什么。</t>
-  </si>
-  <si>
-    <t>Brief section 2 - prioritised backlog, shared Definition of Done
-规范第 2 节 —— 按优先级排序的待办列表，共享的完成定义</t>
-  </si>
-  <si>
-    <t>This workbook, committed as docs/UFCEP6-0-3_Product-Backlog.xlsx
-本工作簿，作为 docs/UFCEP6-0-3_Product-Backlog.xlsx 提交</t>
+    <t>Product backlog and Definition of Done</t>
+  </si>
+  <si>
+    <t>Every item has a first owner, a second owner, an estimate, acceptance conditions and a dependency.</t>
+  </si>
+  <si>
+    <t>Write the full list of work, and agree what 'finished' means on this project.</t>
+  </si>
+  <si>
+    <t>Brief section 2 - prioritised backlog, shared Definition of Done</t>
+  </si>
+  <si>
+    <t>This workbook, committed as docs/UFCEP6-0-3_Product-Backlog.xlsx</t>
   </si>
   <si>
     <t>Mj04</t>
   </si>
   <si>
-    <t>Sprint 1 plan
-Sprint 1 计划</t>
-  </si>
-  <si>
-    <t>A written Sprint goal and a Sprint 1 backlog exist, and the estimate fits our capacity.
-有书面的 Sprint 目标与 Sprint 1 待办列表，且总估算在团队产能内。</t>
-  </si>
-  <si>
-    <t>Agree the Sprint 1 goal, how much we can take on, and which items we commit to.
-商定 Sprint 1 的目标、我们能承担多少、以及承诺做哪些条目。</t>
-  </si>
-  <si>
-    <t>Brief section 2 - each Sprint agrees a goal and a controlled Sprint backlog
-规范第 2 节 —— 每个 Sprint 商定目标并选择可控的 Sprint 待办列表</t>
-  </si>
-  <si>
-    <t>docs/sprint-1-plan.md and the Sprint 1 workbook
-docs/sprint-1-plan.md 以及 Sprint 1 工作簿</t>
+    <t>Sprint 1 plan</t>
+  </si>
+  <si>
+    <t>A written Sprint goal and a Sprint 1 backlog exist, and the estimate fits our capacity.</t>
+  </si>
+  <si>
+    <t>Agree the Sprint 1 goal, how much we can take on, and which items we commit to.</t>
+  </si>
+  <si>
+    <t>Brief section 2 - each Sprint agrees a goal and a controlled Sprint backlog</t>
+  </si>
+  <si>
+    <t>docs/sprint-1-plan.md and the Sprint 1 workbook</t>
   </si>
   <si>
     <t>Mj05</t>
   </si>
   <si>
-    <t>Prepare and record standup 1 (SU1)
-准备并记录站会 1（SU1）</t>
-  </si>
-  <si>
-    <t>All four members have a written update covering progress, evidence, next step, blocker and handover.
-四名成员都有书面汇报，覆盖进展、证据、下一步、阻碍和交接。</t>
-  </si>
-  <si>
-    <t>Every member prepares a short update with evidence before the graded standup.
-在计分站会之前，每位成员准备好带证据的简短汇报。</t>
-  </si>
-  <si>
-    <t>Brief section 2 - graded standups; attendance alone scores nothing
-规范第 2 节 —— 计分站会；仅出席不得分</t>
-  </si>
-  <si>
-    <t>Filled standup sheet, plus board and commit links
-填好的站会工作表，外加任务板和提交记录链接</t>
+    <t>Prepare and record standup 1 (SU1)</t>
+  </si>
+  <si>
+    <t>All four members have a written update covering progress, evidence, next step, blocker and handover.</t>
+  </si>
+  <si>
+    <t>Every member prepares a short update with evidence before the graded standup.</t>
+  </si>
+  <si>
+    <t>Brief section 2 - graded standups; attendance alone scores nothing</t>
+  </si>
+  <si>
+    <t>Filled standup sheet, plus board and commit links</t>
   </si>
   <si>
     <t>Mj06</t>
   </si>
   <si>
-    <t>Sprint 1 review demo and snapshot
-Sprint 1 评审演示与快照</t>
-  </si>
-  <si>
-    <t>The BPMN increment runs end to end in front of the tutor, and tag sr1-snapshot is pushed.
-BPMN 增量能在导师面前端到端跑通，且 sr1-snapshot 标签已推送。</t>
-  </si>
-  <si>
-    <t>To Do</t>
-  </si>
-  <si>
-    <t>Demonstrate what actually runs at the end of Sprint 1, and freeze that version.
-在 Sprint 1 结束时演示真正能跑起来的东西，并把这个版本冻结下来。</t>
-  </si>
-  <si>
-    <t>Brief sections 2 and 4 - SR1 is marked on the increment as it stands
-规范第 2 节和第 4 节 —— SR1 按评审当时的增量评分</t>
-  </si>
-  <si>
-    <t>Demo recording, tag sr1-snapshot, feedback notes
-演示录屏、sr1-snapshot 标签、反馈记录</t>
+    <t>Sprint 1 review demo and snapshot</t>
+  </si>
+  <si>
+    <t>The BPMN increment runs end to end in front of the tutor, and tag sr1-snapshot is pushed.</t>
+  </si>
+  <si>
+    <t>Demonstrate what actually runs at the end of Sprint 1, and freeze that version.</t>
+  </si>
+  <si>
+    <t>Brief sections 2 and 4 - SR1 is marked on the increment as it stands</t>
+  </si>
+  <si>
+    <t>Demo recording, tag sr1-snapshot, feedback notes</t>
   </si>
   <si>
     <t>Mj07</t>
   </si>
   <si>
-    <t>Sprint 1 retrospective
-Sprint 1 回顾</t>
-  </si>
-  <si>
-    <t>At least two improvements are agreed, each with an owner and a target Sprint.
-至少商定两项改进，每项都有负责人和目标 Sprint。</t>
-  </si>
-  <si>
-    <t>Short meeting after the review: what worked, what did not, what we change next Sprint.
-评审后开短会：什么做得好、什么不好、下个 Sprint 改什么。</t>
-  </si>
-  <si>
-    <t>Brief section 2 - retrospective after each review
-规范第 2 节 —— 每次评审后举行回顾</t>
+    <t>Sprint 1 retrospective</t>
+  </si>
+  <si>
+    <t>At least two improvements are agreed, each with an owner and a target Sprint.</t>
+  </si>
+  <si>
+    <t>Short meeting after the review: what worked, what did not, what we change next Sprint.</t>
+  </si>
+  <si>
+    <t>Brief section 2 - retrospective after each review</t>
   </si>
   <si>
     <t>docs/retrospective-s1.md
@@ -268,23 +230,19 @@
     <t>Mj08</t>
   </si>
   <si>
-    <t>Sprint 2 plan
-Sprint 2 计划</t>
-  </si>
-  <si>
-    <t>The Sprint 2 goal refers to specific SR1 feedback, and the backlog reflects it.
-Sprint 2 目标明确引用了 SR1 的具体反馈，且待办列表体现了这些反馈。</t>
+    <t>Sprint 2 plan</t>
+  </si>
+  <si>
+    <t>The Sprint 2 goal refers to specific SR1 feedback, and the backlog reflects it.</t>
   </si>
   <si>
     <t>S2</t>
   </si>
   <si>
-    <t>Turn the Sprint 1 feedback into a Sprint 2 goal and backlog.
-把 Sprint 1 的反馈转化成 Sprint 2 的目标和待办列表。</t>
-  </si>
-  <si>
-    <t>Brief section 2 - feedback from each review must shape the next Sprint
-规范第 2 节 —— 每次评审的反馈必须用于指导下个 Sprint</t>
+    <t>Turn the Sprint 1 feedback into a Sprint 2 goal and backlog.</t>
+  </si>
+  <si>
+    <t>Brief section 2 - feedback from each review must shape the next Sprint</t>
   </si>
   <si>
     <t>docs/sprint-2-plan.md
@@ -294,463 +252,364 @@
     <t>Mj09</t>
   </si>
   <si>
-    <t>Prepare and record standup 2 (SU2)
-准备并记录站会 2（SU2）</t>
-  </si>
-  <si>
-    <t>All four members have a written update, including any handover.
-四名成员都有书面汇报，包含交接情况。</t>
-  </si>
-  <si>
-    <t>Same as SU1, and each member also reports on any handover that happened.
-与 SU1 相同，另外每人要汇报发生过的交接。</t>
-  </si>
-  <si>
-    <t>Brief - personal progress, next actions and handover evidence
-规范 —— 个人进展、后续行动及交接的证据</t>
-  </si>
-  <si>
-    <t>Filled standup sheet, board and commit links
-填好的站会工作表、任务板和提交记录链接</t>
+    <t>Prepare and record standup 2 (SU2)</t>
+  </si>
+  <si>
+    <t>All four members have a written update, including any handover.</t>
+  </si>
+  <si>
+    <t>Same as SU1, and each member also reports on any handover that happened.</t>
+  </si>
+  <si>
+    <t>Brief - personal progress, next actions and handover evidence</t>
+  </si>
+  <si>
+    <t>Filled standup sheet, board and commit links</t>
   </si>
   <si>
     <t>Mj10</t>
   </si>
   <si>
-    <t>Sprint 2 review (SR2)
-Sprint 2 评审（SR2）</t>
-  </si>
-  <si>
-    <t>BPMN, workers and forms run together in one demonstration, and tag sr2-snapshot is pushed.
-BPMN、workers 和 forms 在同一次演示中一起跑通，且 sr2-snapshot 标签已推送。</t>
-  </si>
-  <si>
-    <t>Present the integrated increment to the tutor and collect feedback.
-向导师展示集成增量，并收集反馈。</t>
-  </si>
-  <si>
-    <t>Brief section 2 - SR2 is marked on the integrated increment
-规范第 2 节 —— SR2 按集成增量评分</t>
-  </si>
-  <si>
-    <t>Recording, tag sr2-snapshot, feedback notes and the backlog changes it caused
-录屏、sr2-snapshot 标签、反馈记录，以及由此产生的待办列表变更</t>
+    <t>Sprint 2 review (SR2)</t>
+  </si>
+  <si>
+    <t>BPMN, workers and forms run together in one demonstration, and tag sr2-snapshot is pushed.</t>
+  </si>
+  <si>
+    <t>Present the integrated increment to the tutor and collect feedback.</t>
+  </si>
+  <si>
+    <t>Brief section 2 - SR2 is marked on the integrated increment</t>
+  </si>
+  <si>
+    <t>Recording, tag sr2-snapshot, feedback notes and the backlog changes it caused</t>
   </si>
   <si>
     <t>Mj11</t>
   </si>
   <si>
-    <t>Requirements
-需求</t>
-  </si>
-  <si>
-    <t>Functional requirements list
-功能需求清单</t>
-  </si>
-  <si>
-    <t>Every requirement has an ID and can be traced to the process step that satisfies it.
-每条需求都有编号，并能追溯到满足它的流程步骤。</t>
-  </si>
-  <si>
-    <t>Write the numbered functional requirements the system must satisfy, taken from the case study.
-根据案例写出系统必须满足的、带编号的功能需求。</t>
-  </si>
-  <si>
-    <t>Case study - the closing section asks for functional and non-functional requirements
-案例结尾段 —— 要求给出功能性与非功能性需求</t>
-  </si>
-  <si>
-    <t>docs/requirements.md with a traceability column linking to backlog IDs
-docs/requirements.md，含链接到待办编号的追溯列</t>
+    <t>Requirements</t>
+  </si>
+  <si>
+    <t>Functional requirements list</t>
+  </si>
+  <si>
+    <t>Every requirement has an ID and can be traced to the process step that satisfies it.</t>
+  </si>
+  <si>
+    <t>Write the numbered functional requirements the system must satisfy, taken from the case study.</t>
+  </si>
+  <si>
+    <t>Case study - the closing section asks for functional and non-functional requirements</t>
+  </si>
+  <si>
+    <t>docs/requirements.md with a traceability column linking to backlog IDs</t>
   </si>
   <si>
     <t>Mj12</t>
   </si>
   <si>
-    <t>Non-functional requirements
-非功能性需求</t>
-  </si>
-  <si>
-    <t>Each requirement states how it can be tested, not just what it asks for.
-每条需求都写明如何验证，而不只是提出要求。</t>
-  </si>
-  <si>
-    <t>Rules about security, audit trails, availability and accessibility, rather than features.
-关于安全、审计、可用性和无障碍的规定，而不是功能。</t>
-  </si>
-  <si>
-    <t>Case study - access control, audit records, availability, patient accessibility
-案例 —— 访问控制、审计记录、可用性、患者无障碍需求</t>
-  </si>
-  <si>
-    <t>docs/requirements.md, non-functional section
-docs/requirements.md 的非功能性需求部分</t>
+    <t>Non-functional requirements</t>
+  </si>
+  <si>
+    <t>Each requirement states how it can be tested, not just what it asks for.</t>
+  </si>
+  <si>
+    <t>Rules about security, audit trails, availability and accessibility, rather than features.</t>
+  </si>
+  <si>
+    <t>Case study - access control, audit records, availability, patient accessibility</t>
+  </si>
+  <si>
+    <t>docs/requirements.md, non-functional section</t>
   </si>
   <si>
     <t>Mj13</t>
   </si>
   <si>
-    <t>Data and variable dictionary
-数据与变量字典</t>
+    <t>Data and variable dictionary</t>
   </si>
   <si>
     <t>L</t>
   </si>
   <si>
-    <t>Every worker input and output appears in the dictionary, and names match the models exactly.
-worker 的每个输入输出都在字典中，且名称与模型完全一致。</t>
-  </si>
-  <si>
-    <t>List every process variable: its name, type, where it comes from and which task uses it.
-列出每个流程变量：名称、类型、从哪来、哪个任务在使用。</t>
-  </si>
-  <si>
-    <t>Brief - process variables must be exchanged correctly between forms, tasks and workers
-规范 —— 表单、任务和 worker 之间必须正确交换流程变量</t>
-  </si>
-  <si>
-    <t>docs/data-dictionary.md, cross-checked against the deployed models
-docs/data-dictionary.md，已与部署后的模型交叉核对</t>
+    <t>Every worker input and output appears in the dictionary, and names match the models exactly.</t>
+  </si>
+  <si>
+    <t>List every process variable: its name, type, where it comes from and which task uses it.</t>
+  </si>
+  <si>
+    <t>Brief - process variables must be exchanged correctly between forms, tasks and workers</t>
+  </si>
+  <si>
+    <t>docs/data-dictionary.md, cross-checked against the deployed models</t>
   </si>
   <si>
     <t>Mj14</t>
   </si>
   <si>
-    <t>External service interface definitions
-外部服务接口定义</t>
-  </si>
-  <si>
-    <t>Each service has a named input, a named output, and at least one defined failure response.
-每个服务都有明确的输入、输出，以及至少一种已定义的失败响应。</t>
-  </si>
-  <si>
-    <t>Define what we send to and expect back from each simulated external service.
-定义我们给每个模拟外部服务发什么、期望收回什么。</t>
-  </si>
-  <si>
-    <t>Brief task 02 - explain any simulated external service and its limitations
-规范任务 02 —— 说明任何模拟的外部服务及其局限性</t>
-  </si>
-  <si>
-    <t>docs/external-interfaces.md, matching the worker code
-docs/external-interfaces.md，与 worker 代码一致</t>
+    <t>External service interface definitions</t>
+  </si>
+  <si>
+    <t>Each service has a named input, a named output, and at least one defined failure response.</t>
+  </si>
+  <si>
+    <t>Define what we send to and expect back from each simulated external service.</t>
+  </si>
+  <si>
+    <t>Brief task 02 - explain any simulated external service and its limitations</t>
+  </si>
+  <si>
+    <t>docs/external-interfaces.md, matching the worker code</t>
   </si>
   <si>
     <t>Mj15</t>
   </si>
   <si>
-    <t>BPMN
-BPMN 流程建模</t>
-  </si>
-  <si>
-    <t>Multi-pool collaboration diagram
-多 Pool 协作图</t>
-  </si>
-  <si>
-    <t>Every participant named in the case study appears in a pool, and each pool has an owner.
-案例中提到的每个参与方都有对应的池，且每个池在团队内都有负责人。</t>
-  </si>
-  <si>
-    <t>Lay out the participants as separate pools and show the messages that pass between them.
-把各参与方画成独立的池，并画出它们之间传递的消息。</t>
-  </si>
-  <si>
-    <t>Brief task 01 - use multiple pools where independent participants collaborate
-规范任务 01 —— 相互独立的参与者之间协作时使用多个池</t>
-  </si>
-  <si>
-    <t>bpmn/collaboration-overview.bpmn committed
-bpmn/collaboration-overview.bpmn 已提交</t>
+    <t>BPMN</t>
+  </si>
+  <si>
+    <t>Multi-pool collaboration diagram</t>
+  </si>
+  <si>
+    <t>Every participant named in the case study appears in a pool, and each pool has an owner.</t>
+  </si>
+  <si>
+    <t>Lay out the participants as separate pools and show the messages that pass between them.</t>
+  </si>
+  <si>
+    <t>Brief task 01 - use multiple pools where independent participants collaborate</t>
+  </si>
+  <si>
+    <t>bpmn/collaboration-overview.bpmn committed</t>
   </si>
   <si>
     <t>Mj16</t>
   </si>
   <si>
-    <t>Referral intake and document check
-转诊接收与文件检查</t>
-  </si>
-  <si>
-    <t>The model requests missing documents and records the request, and never lets the secretary accept a referral.
-模型能发出索取缺失材料的请求并记录，且秘书无法接受转诊。</t>
-  </si>
-  <si>
-    <t>Model what the secretary does: check the referral pack is complete, and chase what is missing.
-建模医疗秘书的工作：检查转诊材料是否齐全，缺什么就去索取。</t>
-  </si>
-  <si>
-    <t>Case study - the secretary checks completeness but cannot judge clinical suitability
-案例 —— 秘书只检查材料完整性，无权评估临床适宜性</t>
-  </si>
-  <si>
-    <t>bpmn/referral-intake.bpmn plus a screenshot of the completeness gateway
-bpmn/referral-intake.bpmn，外加完整性判断网关的截图</t>
+    <t>Referral intake and document check</t>
+  </si>
+  <si>
+    <t>The model requests missing documents and records the request, and never lets the secretary accept a referral.</t>
+  </si>
+  <si>
+    <t>Model what the secretary does: check the referral pack is complete, and chase what is missing.</t>
+  </si>
+  <si>
+    <t>Case study - the secretary checks completeness but cannot judge clinical suitability</t>
+  </si>
+  <si>
+    <t>bpmn/referral-intake.bpmn plus a screenshot of the completeness gateway</t>
   </si>
   <si>
     <t>Mj17</t>
   </si>
   <si>
-    <t>Consultant clinical review
-顾问医师临床审核</t>
-  </si>
-  <si>
-    <t>All four outcomes are reachable, and the record shows the reason and the consultant's identity.
-四种结果都能走到，且记录显示理由和顾问医师身份。</t>
-  </si>
-  <si>
-    <t>Model the four decisions a consultant can make, and record who decided and why.
-建模顾问医师能做的四种决定，并记录谁决定的、为什么。</t>
-  </si>
-  <si>
-    <t>Case study - accept, reject, request information or redirect; reason and decision maker must be recorded
-案例 —— 接受、拒绝、要求补充或改派；必须记录理由和决定人</t>
-  </si>
-  <si>
-    <t>bpmn/referral-intake.bpmn plus four test runs, one per outcome
-bpmn/referral-intake.bpmn，外加每个结果各一次测试运行</t>
+    <t>Consultant clinical review</t>
+  </si>
+  <si>
+    <t>All four outcomes are reachable, and the record shows the reason and the consultant's identity.</t>
+  </si>
+  <si>
+    <t>Model the four decisions a consultant can make, and record who decided and why.</t>
+  </si>
+  <si>
+    <t>Case study - accept, reject, request information or redirect; reason and decision maker must be recorded</t>
+  </si>
+  <si>
+    <t>bpmn/referral-intake.bpmn plus four test runs, one per outcome</t>
   </si>
   <si>
     <t>Mj18</t>
   </si>
   <si>
-    <t>New patient appointment booking
-新患者预约流程</t>
-  </si>
-  <si>
-    <t>Both notification paths work, every contact attempt is recorded, and no appointment is confirmed without a slot.
-两条通知路径都能走通，每次联系尝试都有记录，未取得时段不得确认预约。</t>
-  </si>
-  <si>
-    <t>Model booking against the external scheduling service, including notification by letter and phone.
-建模通过外部排程服务预约，包括用信件和电话通知患者。</t>
-  </si>
-  <si>
-    <t>Case study - use the external scheduling service; phone as well as letter when the appointment is within two weeks
-案例 —— 使用外部排程服务；预约在两周内时除信件外还须电话联系</t>
-  </si>
-  <si>
-    <t>bpmn/appointment-booking.bpmn plus test runs for letter-only and letter-plus-phone
-bpmn/appointment-booking.bpmn，外加'仅信件'和'信件+电话'两种测试运行</t>
+    <t>New patient appointment booking</t>
+  </si>
+  <si>
+    <t>Both notification paths work, every contact attempt is recorded, and no appointment is confirmed without a slot.</t>
+  </si>
+  <si>
+    <t>Model booking against the external scheduling service, including notification by letter and phone.</t>
+  </si>
+  <si>
+    <t>Case study - use the external scheduling service; phone as well as letter when the appointment is within two weeks</t>
+  </si>
+  <si>
+    <t>bpmn/appointment-booking.bpmn plus test runs for letter-only and letter-plus-phone</t>
   </si>
   <si>
     <t>Mj19</t>
   </si>
   <si>
-    <t>Consent and authorised treatment request
-知情同意与授权治疗申请</t>
-  </si>
-  <si>
-    <t>The process blocks any treatment request that has not been authorised by a clinical role.
-未经临床角色授权的治疗申请，流程会阻止其继续。</t>
-  </si>
-  <si>
-    <t>Model recording consent, then creating a treatment request only a clinician can authorise.
-建模记录知情同意，然后生成一份只有临床人员能授权的治疗申请。</t>
-  </si>
-  <si>
-    <t>Case study - treatment requests must be completed and authorised by a clinical professional
-案例 —— 治疗申请必须由相应临床专业人员填写并授权</t>
-  </si>
-  <si>
-    <t>bpmn/treatment-request.bpmn plus a test run showing the blocked path
-bpmn/treatment-request.bpmn，外加显示被拦截路径的测试运行</t>
+    <t>Consent and authorised treatment request</t>
+  </si>
+  <si>
+    <t>The process blocks any treatment request that has not been authorised by a clinical role.</t>
+  </si>
+  <si>
+    <t>Model recording consent, then creating a treatment request only a clinician can authorise.</t>
+  </si>
+  <si>
+    <t>Case study - treatment requests must be completed and authorised by a clinical professional</t>
+  </si>
+  <si>
+    <t>bpmn/treatment-request.bpmn plus a test run showing the blocked path</t>
   </si>
   <si>
     <t>Mj20</t>
   </si>
   <si>
-    <t>Treatment appointment coordination
-治疗预约协调</t>
-  </si>
-  <si>
-    <t>The pending path runs end to end, and repeating the attempt never creates a second booking.
-待处理路径能端到端跑通，重复尝试也不会产生第二个预约。</t>
-  </si>
-  <si>
-    <t>Model coordinating treatment slots, including what happens when an external service is unavailable.
-建模协调治疗时段，包括外部服务不可用时的处理。</t>
-  </si>
-  <si>
-    <t>Case study - hold pending, notify, record retries, and do not create a duplicate booking
-案例 —— 保持待处理、通知负责团队、记录后续尝试，且不得产生重复预约</t>
-  </si>
-  <si>
-    <t>bpmn/treatment-booking.bpmn plus a test that retries twice and shows one booking
-bpmn/treatment-booking.bpmn，外加重试两次仍只有一个预约的测试</t>
+    <t>Treatment appointment coordination</t>
+  </si>
+  <si>
+    <t>The pending path runs end to end, and repeating the attempt never creates a second booking.</t>
+  </si>
+  <si>
+    <t>Model coordinating treatment slots, including what happens when an external service is unavailable.</t>
+  </si>
+  <si>
+    <t>Case study - hold pending, notify, record retries, and do not create a duplicate booking</t>
+  </si>
+  <si>
+    <t>bpmn/treatment-booking.bpmn plus a test that retries twice and shows one booking</t>
   </si>
   <si>
     <t>Mj21</t>
   </si>
   <si>
-    <t>Funding check and approval
-资金检查与批准</t>
-  </si>
-  <si>
-    <t>All three funding outcomes are reachable and each approval records the four required fields.
-三种资金来源结果都能走到，且每次审批都记录四项必需字段。</t>
-  </si>
-  <si>
-    <t>Work out who pays: the hospital, an insurer, or the patient, and record the approval details.
-判断由谁付费：医院、保险机构还是患者本人，并记录审批细节。</t>
-  </si>
-  <si>
-    <t>Case study - record the funding body, authorisation number, approved amount and any restrictions
-案例 —— 记录资助机构、授权编号、批准金额及任何限制</t>
-  </si>
-  <si>
-    <t>bpmn/funding.bpmn plus test runs for each funding source
-bpmn/funding.bpmn，外加每种资金来源各一次测试运行</t>
+    <t>Funding check and approval</t>
+  </si>
+  <si>
+    <t>All three funding outcomes are reachable and each approval records the four required fields.</t>
+  </si>
+  <si>
+    <t>Work out who pays: the hospital, an insurer, or the patient, and record the approval details.</t>
+  </si>
+  <si>
+    <t>Case study - record the funding body, authorisation number, approved amount and any restrictions</t>
+  </si>
+  <si>
+    <t>bpmn/funding.bpmn plus test runs for each funding source</t>
   </si>
   <si>
     <t>Mj22</t>
   </si>
   <si>
-    <t>Payment process
-支付流程</t>
-  </si>
-  <si>
-    <t>Each failure outcome can be produced, and a retry never produces a second charge.
-每种失败结果都能复现，且重试不会产生第二笔收费。</t>
-  </si>
-  <si>
-    <t>Model taking payment through the external provider, including every way it can go wrong.
-建模通过外部支付服务收款，包含所有可能出错的情况。</t>
-  </si>
-  <si>
-    <t>Case study - declined, cancelled, duplicate and never-completed payments; never charge twice
-案例 —— 拒绝、取消、重复和始终未完成的付款；不得重复收费</t>
-  </si>
-  <si>
-    <t>bpmn/payment.bpmn plus test runs for declined, duplicate and retry
-bpmn/payment.bpmn，外加拒绝、重复、重试三种测试运行</t>
+    <t>Payment process</t>
+  </si>
+  <si>
+    <t>Each failure outcome can be produced, and a retry never produces a second charge.</t>
+  </si>
+  <si>
+    <t>Model taking payment through the external provider, including every way it can go wrong.</t>
+  </si>
+  <si>
+    <t>Case study - declined, cancelled, duplicate and never-completed payments; never charge twice</t>
+  </si>
+  <si>
+    <t>bpmn/payment.bpmn plus test runs for declined, duplicate and retry</t>
   </si>
   <si>
     <t>Mj23</t>
   </si>
   <si>
-    <t>Refund process
-退款流程</t>
+    <t>Refund process</t>
   </si>
   <si>
     <t>P1</t>
   </si>
   <si>
-    <t>The model prevents a clinical-only role from approving a refund.
-模型能阻止仅有临床权限的角色批准退款。</t>
-  </si>
-  <si>
-    <t>Model refunds when treatment is cancelled or changed, approved only by finance.
-建模治疗取消或变更时的退款，且只能由财务批准。</t>
-  </si>
-  <si>
-    <t>Case study - finance decides refunds; clinical staff cannot approve them without finance authority
-案例 —— 由财务决定退款；临床人员无财务权限不得批准</t>
-  </si>
-  <si>
-    <t>bpmn/refund.bpmn plus a test run showing the blocked approval
-bpmn/refund.bpmn，外加显示审批被拦截的测试运行</t>
+    <t>The model prevents a clinical-only role from approving a refund.</t>
+  </si>
+  <si>
+    <t>Model refunds when treatment is cancelled or changed, approved only by finance.</t>
+  </si>
+  <si>
+    <t>Case study - finance decides refunds; clinical staff cannot approve them without finance authority</t>
+  </si>
+  <si>
+    <t>bpmn/refund.bpmn plus a test run showing the blocked approval</t>
   </si>
   <si>
     <t>Mj24</t>
   </si>
   <si>
-    <t>Chemotherapy cycles and treatment changes
-化疗周期与治疗变更</t>
-  </si>
-  <si>
-    <t>A change requested outside the system cannot be processed, and the clinical outcome is recorded.
-系统之外提出的变更无法被处理，且临床结果有记录。</t>
-  </si>
-  <si>
-    <t>Model the review before each cycle, and the formal process for changing a treatment plan.
-建模每个周期前的复查，以及变更治疗方案的正式流程。</t>
-  </si>
-  <si>
-    <t>Case study - clinical review and blood tests before each cycle; changes need a formal authorised request, not an email
-案例 —— 每周期前临床复查与血检；变更须正式授权申请，邮件或电话无效</t>
-  </si>
-  <si>
-    <t>bpmn/treatment-change.bpmn plus test runs for a cycle review and a formal change
-bpmn/treatment-change.bpmn，外加周期复查与正式变更的测试运行</t>
+    <t>Chemotherapy cycles and treatment changes</t>
+  </si>
+  <si>
+    <t>A change requested outside the system cannot be processed, and the clinical outcome is recorded.</t>
+  </si>
+  <si>
+    <t>Model the review before each cycle, and the formal process for changing a treatment plan.</t>
+  </si>
+  <si>
+    <t>Case study - clinical review and blood tests before each cycle; changes need a formal authorised request, not an email</t>
+  </si>
+  <si>
+    <t>bpmn/treatment-change.bpmn plus test runs for a cycle review and a formal change</t>
   </si>
   <si>
     <t>Mj25</t>
   </si>
   <si>
-    <t>Outpatient letter and escalation
-门诊信函流程与升级</t>
-  </si>
-  <si>
-    <t>All three escalation levels are reachable and the timer dates can be demonstrated.
-三个升级层级都能走到，且计时日期可以演示。</t>
-  </si>
-  <si>
-    <t>Model writing, approving and sending the letter, and chasing it when it is late.
-建模信函的撰写、批准、寄出，以及超期后的催办升级。</t>
-  </si>
-  <si>
-    <t>Case study - letter within seven days; weekly reminder; escalate at one month and three months
-案例 —— 七天内完成信函；之后每周提醒；满一个月和三个月分别上报</t>
-  </si>
-  <si>
-    <t>bpmn/outpatient-letter.bpmn plus test runs at day 7, day 30 and day 90
-bpmn/outpatient-letter.bpmn，外加第 7 天、第 30 天、第 90 天的测试运行</t>
+    <t>Outpatient letter and escalation</t>
+  </si>
+  <si>
+    <t>All three escalation levels are reachable and the timer dates can be demonstrated.</t>
+  </si>
+  <si>
+    <t>Model writing, approving and sending the letter, and chasing it when it is late.</t>
+  </si>
+  <si>
+    <t>Case study - letter within seven days; weekly reminder; escalate at one month and three months</t>
+  </si>
+  <si>
+    <t>bpmn/outpatient-letter.bpmn plus test runs at day 7, day 30 and day 90</t>
   </si>
   <si>
     <t>Mj26</t>
   </si>
   <si>
-    <t>Follow-up, cancellation and no-show
-随访、取消与未出席</t>
-  </si>
-  <si>
-    <t>If no slot matches the clinical timeframe, the case is flagged rather than quietly booked late.
-若找不到符合临床时限的时段，病例会被标示出来，而不是悄悄延后预约。</t>
-  </si>
-  <si>
-    <t>Model follow-up requests, and what happens when a patient cancels, refuses or does not attend.
-建模随访请求，以及患者取消、拒绝或未到诊时的处理。</t>
-  </si>
-  <si>
-    <t>Case study - record the event, decide the next step, and refer paid appointments to finance
-案例 —— 记录事件、决定下一步，已付费预约须转财务</t>
-  </si>
-  <si>
-    <t>bpmn/follow-up.bpmn plus a test run for no slot within the clinical timeframe
-bpmn/follow-up.bpmn，外加临床时限内无可用时段的测试运行</t>
+    <t>Follow-up, cancellation and no-show</t>
+  </si>
+  <si>
+    <t>If no slot matches the clinical timeframe, the case is flagged rather than quietly booked late.</t>
+  </si>
+  <si>
+    <t>Model follow-up requests, and what happens when a patient cancels, refuses or does not attend.</t>
+  </si>
+  <si>
+    <t>Case study - record the event, decide the next step, and refer paid appointments to finance</t>
+  </si>
+  <si>
+    <t>bpmn/follow-up.bpmn plus a test run for no slot within the clinical timeframe</t>
   </si>
   <si>
     <t>Mj27</t>
   </si>
   <si>
-    <t>Enquiry classification and routing
-查询分类与转交</t>
-  </si>
-  <si>
-    <t>A clinical enquiry cannot be closed by a non-clinical role, and every enquiry has a resolution record.
-临床类咨询无法由非临床角色关闭，且每条咨询都有处理结果记录。</t>
-  </si>
-  <si>
-    <t>Model logging a patient enquiry and routing it to admin, finance or clinical.
-建模记录患者咨询，并转交到行政、财务或临床。</t>
-  </si>
-  <si>
-    <t>Case study - the telephone team must not give clinical advice; record time, handler and outcome
-案例 —— 电话接听人员不得提供临床建议；须记录接收时间、处理人和结果</t>
-  </si>
-  <si>
-    <t>bpmn/enquiry.bpmn plus one test run per enquiry type
-bpmn/enquiry.bpmn，外加每种咨询类型各一次测试运行</t>
+    <t>Enquiry classification and routing</t>
+  </si>
+  <si>
+    <t>A clinical enquiry cannot be closed by a non-clinical role, and every enquiry has a resolution record.</t>
+  </si>
+  <si>
+    <t>Model logging a patient enquiry and routing it to admin, finance or clinical.</t>
+  </si>
+  <si>
+    <t>Case study - the telephone team must not give clinical advice; record time, handler and outcome</t>
+  </si>
+  <si>
+    <t>bpmn/enquiry.bpmn plus one test run per enquiry type</t>
   </si>
   <si>
     <t>Mj28</t>
   </si>
   <si>
-    <t>BPMN configuration, deployment and variable mapping
-BPMN 配置、部署与变量映射</t>
-  </si>
-  <si>
-    <t>Every model deploys without error, and the variable names match the data dictionary.
-每个模型都能无错部署，且变量名与数据字典一致。</t>
+    <t>BPMN configuration, deployment and variable mapping</t>
+  </si>
+  <si>
+    <t>Every model deploys without error, and the variable names match the data dictionary.</t>
   </si>
   <si>
     <t>Mj15-27</t>
@@ -759,553 +618,433 @@
     <t>S1/S2</t>
   </si>
   <si>
-    <t>Make the models deployable and check the variables line up across models, forms and workers.
-让模型可部署，并检查变量在模型、表单和 worker 之间对得上。</t>
-  </si>
-  <si>
-    <t>Brief task 01 - configure the model for deployment
-规范任务 01 —— 为部署配置模型</t>
-  </si>
-  <si>
-    <t>config/deployment.md and the deployment log
-config/deployment.md 以及部署日志</t>
+    <t>Make the models deployable and check the variables line up across models, forms and workers.</t>
+  </si>
+  <si>
+    <t>Brief task 01 - configure the model for deployment</t>
+  </si>
+  <si>
+    <t>config/deployment.md and the deployment log</t>
   </si>
   <si>
     <t>Mj29</t>
   </si>
   <si>
-    <t>Workers
-外部 Workers</t>
-  </si>
-  <si>
-    <t>External scheduling worker
-外部排程 Worker</t>
-  </si>
-  <si>
-    <t>Given a specialty and priority, it returns at least one slot or a clear 'none available' result.
-输入专科和优先级后，它返回至少一个时段，或明确返回'无可用时段'。</t>
-  </si>
-  <si>
-    <t>A small program that asks the scheduling service for an available slot.
-一个小程序，向排程服务询问有没有可用时段。</t>
-  </si>
-  <si>
-    <t>Brief task 02 - workers fetch work, use input variables and return results
-规范任务 02 —— worker 获取工作、使用输入变量并返回结果</t>
-  </si>
-  <si>
-    <t>workers/scheduling-worker.js plus a log of one successful and one failed lookup
-workers/scheduling-worker.js，外加一次成功和一次失败的查询日志</t>
+    <t>Workers</t>
+  </si>
+  <si>
+    <t>External scheduling worker</t>
+  </si>
+  <si>
+    <t>Given a specialty and priority, it returns at least one slot or a clear 'none available' result.</t>
+  </si>
+  <si>
+    <t>A small program that asks the scheduling service for an available slot.</t>
+  </si>
+  <si>
+    <t>Brief task 02 - workers fetch work, use input variables and return results</t>
+  </si>
+  <si>
+    <t>workers/scheduling-worker.js plus a log of one successful and one failed lookup</t>
   </si>
   <si>
     <t>Mj30</t>
   </si>
   <si>
-    <t>External communication worker
-外部通信 Worker</t>
-  </si>
-  <si>
-    <t>The worker returns a delivery status, and a failed call is recorded without stopping the process.
-worker 返回送达状态；联系失败会被记录，但不会中断流程。</t>
-  </si>
-  <si>
-    <t>A worker that sends the letter and records the outcome of a telephone call.
-一个 worker，负责发送信件并记录电话联系的结果。</t>
-  </si>
-  <si>
-    <t>Case study - every contact attempt and its outcome must be recorded
-案例 —— 每次联系尝试及其结果都必须记录</t>
-  </si>
-  <si>
-    <t>workers/communication-worker.js plus logs for a delivered letter and an unanswered call
-workers/communication-worker.js，外加信件已送达和电话无人接听的日志</t>
+    <t>External communication worker</t>
+  </si>
+  <si>
+    <t>The worker returns a delivery status, and a failed call is recorded without stopping the process.</t>
+  </si>
+  <si>
+    <t>A worker that sends the letter and records the outcome of a telephone call.</t>
+  </si>
+  <si>
+    <t>Case study - every contact attempt and its outcome must be recorded</t>
+  </si>
+  <si>
+    <t>workers/communication-worker.js plus logs for a delivered letter and an unanswered call</t>
   </si>
   <si>
     <t>Mj31</t>
   </si>
   <si>
-    <t>External payment worker
-外部支付 Worker</t>
-  </si>
-  <si>
-    <t>The worker returns all four fields, and no card number is written to a log or a variable.
-worker 返回全部四个字段，且日志和变量中都不出现卡号。</t>
-  </si>
-  <si>
-    <t>A worker that sends a payment request and returns the provider's answer.
-一个 worker，发送付款请求并返回支付服务商的答复。</t>
-  </si>
-  <si>
-    <t>Case study - the provider returns status, reference, date and amount; no full card details
-案例 —— 服务商返回状态、参考号、日期和金额；不得存储完整卡信息</t>
-  </si>
-  <si>
-    <t>workers/payment-worker.js plus a log check showing no card data
-workers/payment-worker.js，外加显示无卡数据的日志检查</t>
+    <t>External payment worker</t>
+  </si>
+  <si>
+    <t>The worker returns all four fields, and no card number is written to a log or a variable.</t>
+  </si>
+  <si>
+    <t>A worker that sends a payment request and returns the provider's answer.</t>
+  </si>
+  <si>
+    <t>Case study - the provider returns status, reference, date and amount; no full card details</t>
+  </si>
+  <si>
+    <t>workers/payment-worker.js plus a log check showing no card data</t>
   </si>
   <si>
     <t>Mj32</t>
   </si>
   <si>
-    <t>Laboratory and imaging worker
-实验室与影像 Worker</t>
-  </si>
-  <si>
-    <t>The worker returns either a result or an 'unavailable' response, and both are handled.
-worker 返回结果或'不可用'响应，两种情况都有处理。</t>
-  </si>
-  <si>
-    <t>A worker that simulates ordering a test and getting a result back.
-一个 worker，模拟下单检验并取回结果。</t>
-  </si>
-  <si>
-    <t>Case study - blood tests before each chemotherapy cycle
-案例 —— 每次化疗周期前需要血检</t>
-  </si>
-  <si>
-    <t>workers/lab-worker.js plus logs for both outcomes
-workers/lab-worker.js，外加两种结果的日志</t>
+    <t>Laboratory and imaging worker</t>
+  </si>
+  <si>
+    <t>The worker returns either a result or an 'unavailable' response, and both are handled.</t>
+  </si>
+  <si>
+    <t>A worker that simulates ordering a test and getting a result back.</t>
+  </si>
+  <si>
+    <t>Case study - blood tests before each chemotherapy cycle</t>
+  </si>
+  <si>
+    <t>workers/lab-worker.js plus logs for both outcomes</t>
   </si>
   <si>
     <t>Mj33</t>
   </si>
   <si>
-    <t>Error handling, retry and idempotency
-错误处理、重试与幂等</t>
-  </si>
-  <si>
-    <t>Invalid input and timeout are handled, and running the same job twice produces one booking.
-无效输入和超时都有处理，同一任务跑两次只产生一个预约。</t>
+    <t>Error handling, retry and idempotency</t>
+  </si>
+  <si>
+    <t>Invalid input and timeout are handled, and running the same job twice produces one booking.</t>
   </si>
   <si>
     <t>Mj29-32</t>
   </si>
   <si>
-    <t>Make the workers behave sensibly when something goes wrong, and never act twice on the same job.
-让 worker 在出错时表现合理，且对同一个任务绝不重复执行。</t>
-  </si>
-  <si>
-    <t>Case study - retry without creating a duplicate booking or a duplicate charge
-案例 —— 重试时不得产生重复预约或重复收费</t>
-  </si>
-  <si>
-    <t>workers/error-handling.md plus test logs for invalid input, timeout and duplicate delivery
-workers/error-handling.md，外加无效输入、超时、重复投递的测试日志</t>
+    <t>Make the workers behave sensibly when something goes wrong, and never act twice on the same job.</t>
+  </si>
+  <si>
+    <t>Case study - retry without creating a duplicate booking or a duplicate charge</t>
+  </si>
+  <si>
+    <t>workers/error-handling.md plus test logs for invalid input, timeout and duplicate delivery</t>
   </si>
   <si>
     <t>Mj34</t>
   </si>
   <si>
-    <t>Worker configuration and secret template
-Worker 配置与密钥模板</t>
-  </si>
-  <si>
-    <t>No credential appears in the source, and a new machine can be configured from the template alone.
-源码中不出现任何密钥，新机器仅凭模板即可完成配置。</t>
-  </si>
-  <si>
-    <t>Keep connection settings and credentials out of the code.
-把连接配置和密钥从代码里拿出去。</t>
-  </si>
-  <si>
-    <t>Brief task 02 - provide configuration management evidence
-规范任务 02 —— 提供配置管理证据</t>
-  </si>
-  <si>
-    <t>config/.env.example and CONTRIBUTING.md plus a secret scan of the repository
-config/.env.example 和 CONTRIBUTING.md，外加一次仓库密钥扫描</t>
+    <t>Worker configuration and secret template</t>
+  </si>
+  <si>
+    <t>No credential appears in the source, and a new machine can be configured from the template alone.</t>
+  </si>
+  <si>
+    <t>Keep connection settings and credentials out of the code.</t>
+  </si>
+  <si>
+    <t>Brief task 02 - provide configuration management evidence</t>
+  </si>
+  <si>
+    <t>config/.env.example and CONTRIBUTING.md plus a secret scan of the repository</t>
   </si>
   <si>
     <t>Mj35</t>
   </si>
   <si>
-    <t>Worker unit and integration tests
-Worker 单元与集成测试</t>
-  </si>
-  <si>
-    <t>Each worker has at least one passing test for normal and one for failure behaviour.
-每个 worker 至少有一个正常用例和一个失败用例通过。</t>
+    <t>Worker unit and integration tests</t>
+  </si>
+  <si>
+    <t>Each worker has at least one passing test for normal and one for failure behaviour.</t>
   </si>
   <si>
     <t>Mj29-33</t>
   </si>
   <si>
-    <t>Automated tests that prove each worker behaves correctly, including when things fail.
-自动化测试，证明每个 worker 行为正确，包括出错时。</t>
-  </si>
-  <si>
-    <t>Brief task 02 - provide evidence of appropriate testing
-规范任务 02 —— 提供已进行适当测试的证据</t>
-  </si>
-  <si>
-    <t>Test files in workers/test/ and a saved test run output
-workers/test/ 下的测试文件，以及保存的测试运行输出</t>
+    <t>Automated tests that prove each worker behaves correctly, including when things fail.</t>
+  </si>
+  <si>
+    <t>Brief task 02 - provide evidence of appropriate testing</t>
+  </si>
+  <si>
+    <t>Test files in workers/test/ and a saved test run output</t>
   </si>
   <si>
     <t>Mj36</t>
   </si>
   <si>
-    <t>Forms
-Camunda 表单</t>
-  </si>
-  <si>
-    <t>Referral document check form
-转诊文件检查表单</t>
-  </si>
-  <si>
-    <t>The form marks each document present or missing, and contains no field judging clinical suitability.
-表单逐项标记材料齐或缺，且不包含任何评估临床适宜性的字段。</t>
-  </si>
-  <si>
-    <t>The form the secretary fills in to record which documents arrived and which are missing.
-秘书用来记录哪些材料到了、哪些缺的表单。</t>
-  </si>
-  <si>
-    <t>Case study - the secretary can request missing information but cannot assess clinical suitability
-案例 —— 秘书可索取缺失信息，但无权评估临床适宜性</t>
-  </si>
-  <si>
-    <t>forms/referral-check.form plus a screenshot of the rendered form
-forms/referral-check.form，外加表单渲染截图</t>
+    <t>Forms</t>
+  </si>
+  <si>
+    <t>Referral document check form</t>
+  </si>
+  <si>
+    <t>The form marks each document present or missing, and contains no field judging clinical suitability.</t>
+  </si>
+  <si>
+    <t>The form the secretary fills in to record which documents arrived and which are missing.</t>
+  </si>
+  <si>
+    <t>Case study - the secretary can request missing information but cannot assess clinical suitability</t>
+  </si>
+  <si>
+    <t>forms/referral-check.form plus a screenshot of the rendered form</t>
   </si>
   <si>
     <t>Mj37</t>
   </si>
   <si>
-    <t>Consultant review form
-顾问审核表单</t>
-  </si>
-  <si>
-    <t>Decision and reason are mandatory, and the submitting user is captured.
-决定和理由为必填，且提交人身份被记录。</t>
-  </si>
-  <si>
-    <t>The form the consultant uses to record the decision, the reason and who they are.
-顾问用来记录决定、理由和本人身份的表单。</t>
-  </si>
-  <si>
-    <t>Case study - reason and decision maker identity must be recorded
-案例 —— 必须记录决定理由和决定人身份</t>
-  </si>
-  <si>
-    <t>forms/consultant-review.form plus a screenshot
-forms/consultant-review.form，外加截图</t>
+    <t>Consultant review form</t>
+  </si>
+  <si>
+    <t>Decision and reason are mandatory, and the submitting user is captured.</t>
+  </si>
+  <si>
+    <t>The form the consultant uses to record the decision, the reason and who they are.</t>
+  </si>
+  <si>
+    <t>Case study - reason and decision maker identity must be recorded</t>
+  </si>
+  <si>
+    <t>forms/consultant-review.form plus a screenshot</t>
   </si>
   <si>
     <t>Mj38</t>
   </si>
   <si>
-    <t>Appointment and contact record form
-预约与联系记录表单</t>
-  </si>
-  <si>
-    <t>Multiple contact attempts can be recorded against one appointment.
-一次预约下可以记录多次联系尝试。</t>
-  </si>
-  <si>
-    <t>The form for priority, preferred window and the outcome of each contact attempt.
-用于填写优先级、首选时间范围和每次联系结果的表单。</t>
-  </si>
-  <si>
-    <t>Case study - record every contact attempt and its result
-案例 —— 每次联系尝试及其结果都要记录</t>
-  </si>
-  <si>
-    <t>forms/appointment-contact.form plus a screenshot showing two attempts
-forms/appointment-contact.form，外加显示两次尝试的截图</t>
+    <t>Appointment and contact record form</t>
+  </si>
+  <si>
+    <t>Multiple contact attempts can be recorded against one appointment.</t>
+  </si>
+  <si>
+    <t>The form for priority, preferred window and the outcome of each contact attempt.</t>
+  </si>
+  <si>
+    <t>Case study - record every contact attempt and its result</t>
+  </si>
+  <si>
+    <t>forms/appointment-contact.form plus a screenshot showing two attempts</t>
   </si>
   <si>
     <t>Mj39</t>
   </si>
   <si>
-    <t>Treatment request form
-治疗申请表单</t>
-  </si>
-  <si>
-    <t>All six fields are present and validated, and the form cannot be submitted without an authorising clinician.
-六个字段齐全且有验证，且未经临床人员授权无法提交。</t>
-  </si>
-  <si>
-    <t>The form a clinician completes to authorise treatment.
-临床人员用来授权治疗的填写表单。</t>
-  </si>
-  <si>
-    <t>Case study - the request states treatment, start date, cycles, frequency, reviews and special resources
-案例 —— 申请需说明治疗、开始日期、周期、频率、复查和特殊资源</t>
-  </si>
-  <si>
-    <t>forms/treatment-request.form plus a screenshot
-forms/treatment-request.form，外加截图</t>
+    <t>Treatment request form</t>
+  </si>
+  <si>
+    <t>All six fields are present and validated, and the form cannot be submitted without an authorising clinician.</t>
+  </si>
+  <si>
+    <t>The form a clinician completes to authorise treatment.</t>
+  </si>
+  <si>
+    <t>Case study - the request states treatment, start date, cycles, frequency, reviews and special resources</t>
+  </si>
+  <si>
+    <t>forms/treatment-request.form plus a screenshot</t>
   </si>
   <si>
     <t>Mj40</t>
   </si>
   <si>
-    <t>Funding approval form
-资金批准表单</t>
-  </si>
-  <si>
-    <t>All four fields are captured, and the amount is validated as a positive number.
-四个字段都被采集，且金额验证为正数。</t>
-  </si>
-  <si>
-    <t>The form finance completes to record who is paying and under what conditions.
-财务用来记录由谁付费、附带什么条件的表单。</t>
-  </si>
-  <si>
-    <t>Case study - record funding body, authorisation number, approved amount and restrictions
-案例 —— 记录资助机构、授权编号、批准金额和限制</t>
-  </si>
-  <si>
-    <t>forms/funding-approval.form plus a screenshot
-forms/funding-approval.form，外加截图</t>
+    <t>Funding approval form</t>
+  </si>
+  <si>
+    <t>All four fields are captured, and the amount is validated as a positive number.</t>
+  </si>
+  <si>
+    <t>The form finance completes to record who is paying and under what conditions.</t>
+  </si>
+  <si>
+    <t>Case study - record funding body, authorisation number, approved amount and restrictions</t>
+  </si>
+  <si>
+    <t>forms/funding-approval.form plus a screenshot</t>
   </si>
   <si>
     <t>Mj41</t>
   </si>
   <si>
-    <t>Payment form and status
-支付表单与状态</t>
-  </si>
-  <si>
-    <t>No field accepts a full card number, and the payment status is shown after submission.
-没有任何字段接受完整卡号，且提交后显示支付状态。</t>
-  </si>
-  <si>
-    <t>The payment screen. It must never ask for or store full card details.
-支付界面。绝不能索取或存储完整卡信息。</t>
-  </si>
-  <si>
-    <t>Case study - the system must not store full card details
-案例 —— 系统不得存储完整卡信息</t>
-  </si>
-  <si>
-    <t>forms/payment.form, a screenshot, and a note explaining how card data is avoided
-forms/payment.form、截图，以及说明如何规避卡数据的说明</t>
+    <t>Payment form and status</t>
+  </si>
+  <si>
+    <t>No field accepts a full card number, and the payment status is shown after submission.</t>
+  </si>
+  <si>
+    <t>The payment screen. It must never ask for or store full card details.</t>
+  </si>
+  <si>
+    <t>Case study - the system must not store full card details</t>
+  </si>
+  <si>
+    <t>forms/payment.form, a screenshot, and a note explaining how card data is avoided</t>
   </si>
   <si>
     <t>Mj42</t>
   </si>
   <si>
-    <t>Treatment change form
-治疗变更表单</t>
-  </si>
-  <si>
-    <t>The form captures the authorising clinician and the effect on existing costs.
-表单采集授权临床人员信息以及变更对现有费用的影响。</t>
-  </si>
-  <si>
-    <t>The formal form for changing a treatment plan, replacing email and phone requests.
-用于正式变更治疗方案的表格，替代邮件和电话请求。</t>
-  </si>
-  <si>
-    <t>Case study - changes requested by email or phone must not be processed
-案例 —— 通过邮件或电话提出的变更不得处理</t>
-  </si>
-  <si>
-    <t>forms/treatment-change.form plus a screenshot
-forms/treatment-change.form，外加截图</t>
+    <t>Treatment change form</t>
+  </si>
+  <si>
+    <t>The form captures the authorising clinician and the effect on existing costs.</t>
+  </si>
+  <si>
+    <t>The formal form for changing a treatment plan, replacing email and phone requests.</t>
+  </si>
+  <si>
+    <t>Case study - changes requested by email or phone must not be processed</t>
+  </si>
+  <si>
+    <t>forms/treatment-change.form plus a screenshot</t>
   </si>
   <si>
     <t>Mj43</t>
   </si>
   <si>
-    <t>Letter approval and admin check form
-信函批准与行政检查表单</t>
-  </si>
-  <si>
-    <t>After clinical approval the clinical fields become read-only, and a letter can be sent back.
-临床批准后临床字段变为只读，且可以把信函退回。</t>
-  </si>
-  <si>
-    <t>Two steps in one screen: the consultant approves the clinical content, then the secretary checks the administration.
-同一界面上的两步：顾问批准临床内容，秘书做行政核查。</t>
-  </si>
-  <si>
-    <t>Case study - admin can fix formatting but cannot change clinical meaning; suspected clinical errors go back
-案例 —— 行政可更正格式但不得改变临床含义；疑似临床错误须退回</t>
-  </si>
-  <si>
-    <t>forms/letter-approval.form plus a screenshot of the read-only state
-forms/letter-approval.form，外加只读状态截图</t>
+    <t>Letter approval and admin check form</t>
+  </si>
+  <si>
+    <t>After clinical approval the clinical fields become read-only, and a letter can be sent back.</t>
+  </si>
+  <si>
+    <t>Two steps in one screen: the consultant approves the clinical content, then the secretary checks the administration.</t>
+  </si>
+  <si>
+    <t>Case study - admin can fix formatting but cannot change clinical meaning; suspected clinical errors go back</t>
+  </si>
+  <si>
+    <t>forms/letter-approval.form plus a screenshot of the read-only state</t>
   </si>
   <si>
     <t>Mj44</t>
   </si>
   <si>
-    <t>Enquiry classification form
-查询分类表单</t>
-  </si>
-  <si>
-    <t>All three categories are available, each with a target team, and priority can be set.
-三种分类都可选，每类都对应目标团队，且可设置优先级。</t>
-  </si>
-  <si>
-    <t>The form the telephone team uses to classify an enquiry and route it.
-电话接听团队用来分类并转交咨询的表单。</t>
-  </si>
-  <si>
-    <t>Case study - classify as admin, finance or clinical and route to the right team
-案例 —— 分类为行政、财务或临床，并转交对应团队</t>
-  </si>
-  <si>
-    <t>forms/enquiry.form plus a screenshot
-forms/enquiry.form，外加截图</t>
+    <t>Enquiry classification form</t>
+  </si>
+  <si>
+    <t>All three categories are available, each with a target team, and priority can be set.</t>
+  </si>
+  <si>
+    <t>The form the telephone team uses to classify an enquiry and route it.</t>
+  </si>
+  <si>
+    <t>Case study - classify as admin, finance or clinical and route to the right team</t>
+  </si>
+  <si>
+    <t>forms/enquiry.form plus a screenshot</t>
   </si>
   <si>
     <t>Mj45</t>
   </si>
   <si>
-    <t>Form validation, binding and accessibility
-表单验证、绑定与无障碍</t>
-  </si>
-  <si>
-    <t>Every form has labels, an error message for invalid input, keyboard access and sufficient contrast.
-每个表单都有标签、无效输入的错误提示、键盘可操作且对比度足够。</t>
+    <t>Form validation, binding and accessibility</t>
+  </si>
+  <si>
+    <t>Every form has labels, an error message for invalid input, keyboard access and sufficient contrast.</t>
   </si>
   <si>
     <t>Mj36-44</t>
   </si>
   <si>
-    <t>Go through every form and check it validates, is bound to the right task, and can be used by everyone.
-逐个检查表单：验证是否正确、是否绑定到正确任务、是否人人可用。</t>
-  </si>
-  <si>
-    <t>Brief task 03 - validation, correct variable exchange, accessibility and consistency
-规范任务 03 —— 验证、变量正确交换、无障碍与一致性</t>
-  </si>
-  <si>
-    <t>docs/form-review.md with a checklist per form and screenshots
-docs/form-review.md，含每张表单的检查清单和截图</t>
+    <t>Go through every form and check it validates, is bound to the right task, and can be used by everyone.</t>
+  </si>
+  <si>
+    <t>Brief task 03 - validation, correct variable exchange, accessibility and consistency</t>
+  </si>
+  <si>
+    <t>docs/form-review.md with a checklist per form and screenshots</t>
   </si>
   <si>
     <t>Mj46</t>
   </si>
   <si>
-    <t>Security
-安全与合规</t>
-  </si>
-  <si>
-    <t>Role-based access control
-基于角色的访问控制</t>
-  </si>
-  <si>
-    <t>A role matrix exists, and a test shows a role being refused an action outside its remit.
-有角色权限矩阵，且有测试显示某角色被拒绝执行越权操作。</t>
-  </si>
-  <si>
-    <t>Decide who can see and do what, so staff only reach what their job needs.
-确定谁能看什么、做什么，员工只能接触本岗位所需。</t>
-  </si>
-  <si>
-    <t>Case study - authenticate users and apply role-based access control
-案例 —— 对用户进行身份验证并实施基于角色的访问控制</t>
-  </si>
-  <si>
-    <t>docs/access-control.md with the matrix plus test evidence
-docs/access-control.md，含权限矩阵和测试证据</t>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Role-based access control</t>
+  </si>
+  <si>
+    <t>A role matrix exists, and a test shows a role being refused an action outside its remit.</t>
+  </si>
+  <si>
+    <t>Decide who can see and do what, so staff only reach what their job needs.</t>
+  </si>
+  <si>
+    <t>Case study - authenticate users and apply role-based access control</t>
+  </si>
+  <si>
+    <t>docs/access-control.md with the matrix plus test evidence</t>
   </si>
   <si>
     <t>Mj47</t>
   </si>
   <si>
-    <t>Audit log
-审计日志</t>
-  </si>
-  <si>
-    <t>Referral decisions, consent, letter approval and payment requests all appear in the audit record.
-转诊决定、知情同意、信函批准和付款请求都出现在审计记录中。</t>
-  </si>
-  <si>
-    <t>Record important actions so we can show who did what and when.
-记录重要操作，以便说明谁在什么时候做了什么。</t>
-  </si>
-  <si>
-    <t>Case study - audit records show user, date, time and nature; ordinary users cannot edit them
-案例 —— 审计记录标明用户、日期、时间与操作性质，普通用户不得编辑</t>
-  </si>
-  <si>
-    <t>Screenshots of audit entries in Operate plus docs/audit-design.md
-Operate 中审计条目的截图，外加 docs/audit-design.md</t>
+    <t>Audit log</t>
+  </si>
+  <si>
+    <t>Referral decisions, consent, letter approval and payment requests all appear in the audit record.</t>
+  </si>
+  <si>
+    <t>Record important actions so we can show who did what and when.</t>
+  </si>
+  <si>
+    <t>Case study - audit records show user, date, time and nature; ordinary users cannot edit them</t>
+  </si>
+  <si>
+    <t>Screenshots of audit entries in Operate plus docs/audit-design.md</t>
   </si>
   <si>
     <t>Mj48</t>
   </si>
   <si>
-    <t>Sensitive data protection
-敏感数据保护</t>
-  </si>
-  <si>
-    <t>A review of every model, form and worker finds no stored card data and no unprotected external call.
-对每个模型、表单和 worker 的检查中，未发现存储卡数据或未受保护的外部调用。</t>
-  </si>
-  <si>
-    <t>Make sure we hold no card data or unnecessary financial detail, and that external traffic is protected.
-确保不保存卡数据或不必要的财务细节，且与外部服务的通信受到保护。</t>
-  </si>
-  <si>
-    <t>Case study - do not store full card details; protect information exchanged with external services
-案例 —— 不得存储完整卡信息；保护与外部服务交换的信息</t>
-  </si>
-  <si>
-    <t>docs/data-protection.md plus the secret scan from PB34
-docs/data-protection.md，外加 PB34 的密钥扫描结果</t>
+    <t>Sensitive data protection</t>
+  </si>
+  <si>
+    <t>A review of every model, form and worker finds no stored card data and no unprotected external call.</t>
+  </si>
+  <si>
+    <t>Make sure we hold no card data or unnecessary financial detail, and that external traffic is protected.</t>
+  </si>
+  <si>
+    <t>Case study - do not store full card details; protect information exchanged with external services</t>
+  </si>
+  <si>
+    <t>docs/data-protection.md plus the secret scan from PB34</t>
   </si>
   <si>
     <t>Mj49</t>
   </si>
   <si>
-    <t>Reports
-管理报表</t>
-  </si>
-  <si>
-    <t>Management reports and query views
-管理报表与查询视图</t>
+    <t>Reports</t>
+  </si>
+  <si>
+    <t>Management reports and query views</t>
   </si>
   <si>
     <t>P2</t>
   </si>
   <si>
-    <t>Each requested report can be produced with a date filter, or the gap is recorded as a limitation.
-每份要求的报表都能按日期筛选生成，或把缺口记录为局限性。</t>
-  </si>
-  <si>
-    <t>Deferred</t>
-  </si>
-  <si>
-    <t>The reports managers asked for: referral volumes, waiting times, delayed letters, failed payments and so on.
-管理层要求的报表：转诊量、等待时间、延误信函、失败付款等。</t>
-  </si>
-  <si>
-    <t>Case study - reports on referrals, waiting times, delays, payments and refunds
-案例 —— 转诊、等待时间、延误、付款和退款的报表</t>
-  </si>
-  <si>
-    <t>docs/reports.md plus screenshots or a sample export
-docs/reports.md，外加截图或样例导出</t>
+    <t>Each requested report can be produced with a date filter, or the gap is recorded as a limitation.</t>
+  </si>
+  <si>
+    <t>The reports managers asked for: referral volumes, waiting times, delayed letters, failed payments and so on.</t>
+  </si>
+  <si>
+    <t>Case study - reports on referrals, waiting times, delays, payments and refunds</t>
+  </si>
+  <si>
+    <t>docs/reports.md plus screenshots or a sample export</t>
   </si>
   <si>
     <t>Mj50</t>
   </si>
   <si>
-    <t>Testing
-测试</t>
-  </si>
-  <si>
-    <t>Test plan
-测试计划</t>
-  </si>
-  <si>
-    <t>The plan covers normal, alternative and exception paths, and states entry and exit criteria.
-计划覆盖正常、替代和异常路径，并写明进入与退出标准。</t>
-  </si>
-  <si>
-    <t>Write down what we will test, how, and what counts as a pass.
-写清楚测什么、怎么测、什么算通过。</t>
-  </si>
-  <si>
-    <t>Brief - a detailed test plan; LO5 requires an appropriate test strategy
-规范 —— 详细的测试计划；LO5 要求适当的测试策略</t>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Test plan</t>
+  </si>
+  <si>
+    <t>The plan covers normal, alternative and exception paths, and states entry and exit criteria.</t>
+  </si>
+  <si>
+    <t>Write down what we will test, how, and what counts as a pass.</t>
+  </si>
+  <si>
+    <t>Brief - a detailed test plan; LO5 requires an appropriate test strategy</t>
   </si>
   <si>
     <t>docs/test-plan.md
@@ -1315,72 +1054,58 @@
     <t>Mj51</t>
   </si>
   <si>
-    <t>Test cases and scripts
-测试用例与脚本</t>
-  </si>
-  <si>
-    <t>Every exception path in the case study has at least one test case linked to it.
-案例中的每条异常路径都至少有一个关联的测试用例。</t>
-  </si>
-  <si>
-    <t>Write the individual test cases, including the ones that are meant to fail.
-编写具体的测试用例，包括那些故意让它失败的用例。</t>
-  </si>
-  <si>
-    <t>Brief - create, evaluate and execute test scripts
-规范 —— 创建、评估并执行测试脚本</t>
-  </si>
-  <si>
-    <t>docs/test-cases.md and the automated tests from PB35
-docs/test-cases.md，以及 PB35 的自动化测试</t>
+    <t>Test cases and scripts</t>
+  </si>
+  <si>
+    <t>Every exception path in the case study has at least one test case linked to it.</t>
+  </si>
+  <si>
+    <t>Write the individual test cases, including the ones that are meant to fail.</t>
+  </si>
+  <si>
+    <t>Brief - create, evaluate and execute test scripts</t>
+  </si>
+  <si>
+    <t>docs/test-cases.md and the automated tests from PB35</t>
   </si>
   <si>
     <t>Mj52</t>
   </si>
   <si>
-    <t>End-to-end process testing
-端到端流程测试</t>
-  </si>
-  <si>
-    <t>The main pathway, a payment failure and an external service failure have all been run and recorded.
-主路径、付款失败、外部服务失败三种情况都已运行并有记录。</t>
+    <t>End-to-end process testing</t>
+  </si>
+  <si>
+    <t>The main pathway, a payment failure and an external service failure have all been run and recorded.</t>
   </si>
   <si>
     <t>Mj15-33</t>
   </si>
   <si>
-    <t>Run the whole pathway from referral to outcome, including the awkward cases.
-从头到尾跑完整条路径，包括那些麻烦的情况。</t>
-  </si>
-  <si>
-    <t>Brief tasks 02 and 04 - demonstrate normal, alternative and failure scenarios
-规范任务 02 和 04 —— 演示正常、替代和失败场景</t>
-  </si>
-  <si>
-    <t>docs/e2e-results.md with logs and screenshots for each scenario
-docs/e2e-results.md，含每个场景的日志和截图</t>
+    <t>Run the whole pathway from referral to outcome, including the awkward cases.</t>
+  </si>
+  <si>
+    <t>Brief tasks 02 and 04 - demonstrate normal, alternative and failure scenarios</t>
+  </si>
+  <si>
+    <t>docs/e2e-results.md with logs and screenshots for each scenario</t>
   </si>
   <si>
     <t>Mj53</t>
   </si>
   <si>
-    <t>Form and worker testing
-表单与 Worker 测试</t>
-  </si>
-  <si>
-    <t>Each form's validation rules and each worker's failure handling have been exercised and recorded.
-每个表单的验证规则和每个 worker 的失败处理都经过演练并有记录。</t>
+    <t>Form and worker testing</t>
+  </si>
+  <si>
+    <t>Each form's validation rules and each worker's failure handling have been exercised and recorded.</t>
   </si>
   <si>
     <t>Mj36-45</t>
   </si>
   <si>
-    <t>Check that forms validate correctly and that workers pass variables correctly.
-检查表单验证是否正确、worker 是否正确传递变量。</t>
-  </si>
-  <si>
-    <t>Brief tasks 02 and 03 - evidence of testing for workers and forms
-规范任务 02 和 03 —— worker 和表单的测试证据</t>
+    <t>Check that forms validate correctly and that workers pass variables correctly.</t>
+  </si>
+  <si>
+    <t>Brief tasks 02 and 03 - evidence of testing for workers and forms</t>
   </si>
   <si>
     <t>docs/form-worker-test-results.md
@@ -1390,76 +1115,61 @@
     <t>Mj54</t>
   </si>
   <si>
-    <t>Security, audit and accessibility testing
-安全、审计与无障碍测试</t>
-  </si>
-  <si>
-    <t>An unauthorised action is refused, an audit entry is created, and each form is usable by keyboard only.
-越权操作被拒绝、审计记录生成、每个表单仅用键盘即可操作。</t>
+    <t>Security, audit and accessibility testing</t>
+  </si>
+  <si>
+    <t>An unauthorised action is refused, an audit entry is created, and each form is usable by keyboard only.</t>
   </si>
   <si>
     <t>Mj46-48</t>
   </si>
   <si>
-    <t>Try to break the rules on purpose and see whether the system stops us.
-故意去违反规则，看系统会不会拦住我们。</t>
-  </si>
-  <si>
-    <t>Brief - LO1 accessibility, LO4 security and audit
-规范 —— LO1 无障碍，LO4 安全与审计</t>
-  </si>
-  <si>
-    <t>docs/security-accessibility-results.md with screenshots
-docs/security-accessibility-results.md，含截图</t>
+    <t>Try to break the rules on purpose and see whether the system stops us.</t>
+  </si>
+  <si>
+    <t>Brief - LO1 accessibility, LO4 security and audit</t>
+  </si>
+  <si>
+    <t>docs/security-accessibility-results.md with screenshots</t>
   </si>
   <si>
     <t>Mj55</t>
   </si>
   <si>
-    <t>Defects, regression and test evidence
-缺陷、回归与测试证据</t>
-  </si>
-  <si>
-    <t>Every defect has a status, and a regression run is recorded after the fixes.
-每个缺陷都有状态，且修复后有一次回归测试记录。</t>
+    <t>Defects, regression and test evidence</t>
+  </si>
+  <si>
+    <t>Every defect has a status, and a regression run is recorded after the fixes.</t>
   </si>
   <si>
     <t>Mj52-54</t>
   </si>
   <si>
-    <t>Keep a record of what broke, what we fixed, and re-run tests to prove nothing else broke.
-记录什么东西坏了、怎么修的，并重跑测试证明没弄坏别的。</t>
-  </si>
-  <si>
-    <t>Brief - evaluate test results; quality assurance evidence
-规范 —— 评估测试结果；质量保证证据</t>
-  </si>
-  <si>
-    <t>docs/defect-log.md and the regression run output
-docs/defect-log.md 以及回归测试输出</t>
+    <t>Keep a record of what broke, what we fixed, and re-run tests to prove nothing else broke.</t>
+  </si>
+  <si>
+    <t>Brief - evaluate test results; quality assurance evidence</t>
+  </si>
+  <si>
+    <t>docs/defect-log.md and the regression run output</t>
   </si>
   <si>
     <t>Mj56</t>
   </si>
   <si>
-    <t>Demo
-演示</t>
-  </si>
-  <si>
-    <t>Demo script and scenarios
-演示脚本与场景</t>
-  </si>
-  <si>
-    <t>The script covers a normal, an alternative and a failure scenario, and names a speaker for each part.
-脚本覆盖正常、替代、失败三种场景，并为每部分指定讲解人。</t>
-  </si>
-  <si>
-    <t>Agree what we will show, in what order, and who speaks about which part.
-商定演示什么、按什么顺序、谁讲哪部分。</t>
-  </si>
-  <si>
-    <t>Brief task 04 - representative scenarios, and each member explains their own contribution
-规范任务 04 —— 用有代表性的场景演示，每位成员解释自己的贡献</t>
+    <t>Demo</t>
+  </si>
+  <si>
+    <t>Demo script and scenarios</t>
+  </si>
+  <si>
+    <t>The script covers a normal, an alternative and a failure scenario, and names a speaker for each part.</t>
+  </si>
+  <si>
+    <t>Agree what we will show, in what order, and who speaks about which part.</t>
+  </si>
+  <si>
+    <t>Brief task 04 - representative scenarios, and each member explains their own contribution</t>
   </si>
   <si>
     <t>docs/demo-script.md
@@ -1469,67 +1179,49 @@
     <t>Mj57</t>
   </si>
   <si>
-    <t>Integration rehearsal
-集成彩排</t>
-  </si>
-  <si>
-    <t>The full demo runs twice without failure, and every member can explain the parts they did not build.
-完整演示连跑两次无故障，且每位成员都能解释不是自己做的部分。</t>
-  </si>
-  <si>
-    <t>Run the demo end to end, on one machine, before the real thing.
-在正式演示前，在一台机器上完整跑一遍。</t>
-  </si>
-  <si>
-    <t>Brief task 04 - demonstrate a working integrated initial release
-规范任务 04 —— 演示可运行的集成初始发布版本</t>
-  </si>
-  <si>
-    <t>docs/rehearsal-notes.md with the issues found
-docs/rehearsal-notes.md，含发现的问题</t>
+    <t>Integration rehearsal</t>
+  </si>
+  <si>
+    <t>The full demo runs twice without failure, and every member can explain the parts they did not build.</t>
+  </si>
+  <si>
+    <t>Run the demo end to end, on one machine, before the real thing.</t>
+  </si>
+  <si>
+    <t>Brief task 04 - demonstrate a working integrated initial release</t>
+  </si>
+  <si>
+    <t>docs/rehearsal-notes.md with the issues found</t>
   </si>
   <si>
     <t>Mj58</t>
   </si>
   <si>
-    <t>Submission
-提交</t>
-  </si>
-  <si>
-    <t>Final submission package
-最终提交包</t>
-  </si>
-  <si>
-    <t>All five deliverables are uploaded, and the submitted commit or tag is named in the submission note.
-五项交付物全部上传，且在提交说明中写明所提交的 commit 或标签。</t>
-  </si>
-  <si>
-    <t>Put everything together and upload it to Blackboard, recording which repository version was submitted.
-把全部东西打包上传到 Blackboard，并记录提交的是哪个仓库版本。</t>
-  </si>
-  <si>
-    <t>Brief section 3 - models, workers, forms, plans, demo and the repository version
-规范第 3 节 —— 模型、workers、表单、计划、演示，以及仓库版本</t>
-  </si>
-  <si>
-    <t>Blackboard receipt and docs/submission-record.md
-Blackboard 提交回执，以及 docs/submission-record.md</t>
-  </si>
-  <si>
-    <t>成员
-Member</t>
-  </si>
-  <si>
-    <t>负责条目数
-Items</t>
-  </si>
-  <si>
-    <t>负责 SP
-SP</t>
-  </si>
-  <si>
-    <t>占比
-Share</t>
+    <t>Submission</t>
+  </si>
+  <si>
+    <t>Final submission package</t>
+  </si>
+  <si>
+    <t>All five deliverables are uploaded, and the submitted commit or tag is named in the submission note.</t>
+  </si>
+  <si>
+    <t>Put everything together and upload it to Blackboard, recording which repository version was submitted.</t>
+  </si>
+  <si>
+    <t>Brief section 3 - models, workers, forms, plans, demo and the repository version</t>
+  </si>
+  <si>
+    <t>Blackboard receipt and docs/submission-record.md</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>Items</t>
+  </si>
+  <si>
+    <t>Share</t>
   </si>
   <si>
     <t>Sprint 1 SP</t>
@@ -1538,12 +1230,10 @@
     <t>Sprint 2 SP</t>
   </si>
   <si>
-    <t>第二负责人条目
-Items (2nd)</t>
-  </si>
-  <si>
-    <t>第二负责人 SP
-SP (2nd)</t>
+    <t>Items (2nd)</t>
+  </si>
+  <si>
+    <t>SP (2nd)</t>
   </si>
   <si>
     <t>T
@@ -1562,8 +1252,7 @@
 Lorrey</t>
   </si>
   <si>
-    <t>合计
-TOTAL</t>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1429,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1762,12 +1451,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2103,7 +1786,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -2127,16 +1810,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="5">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
@@ -2145,89 +1828,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2242,9 +1925,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2906,28 +2586,28 @@
       <c r="J7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="8" ht="86" customHeight="1" spans="1:14">
       <c r="A8" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>17</v>
@@ -2942,7 +2622,7 @@
         <v>19</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>52</v>
@@ -2950,28 +2630,28 @@
       <c r="J8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="6" t="s">
-        <v>55</v>
+      <c r="K8" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="9" ht="91" customHeight="1" spans="1:14">
       <c r="A9" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>17</v>
@@ -2986,36 +2666,36 @@
         <v>19</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="10" ht="75" customHeight="1" spans="1:14">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -3030,36 +2710,36 @@
         <v>19</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" s="2" t="s">
+      <c r="M10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="11" ht="91" customHeight="1" spans="1:14">
       <c r="A11" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>17</v>
@@ -3074,36 +2754,36 @@
         <v>19</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L11" s="2" t="s">
+      <c r="M11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="N11" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="12" ht="93" customHeight="1" spans="1:14">
       <c r="A12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>17</v>
@@ -3118,7 +2798,7 @@
         <v>29</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>27</v>
@@ -3126,28 +2806,28 @@
       <c r="J12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="6" t="s">
-        <v>55</v>
+      <c r="K12" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M12" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="N12" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="13" ht="92" customHeight="1" spans="1:14">
       <c r="A13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>17</v>
@@ -3162,36 +2842,36 @@
         <v>18</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="I13" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L13" s="2" t="s">
+      <c r="M13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="N13" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="14" ht="90" customHeight="1" spans="1:14">
       <c r="A14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>17</v>
@@ -3200,42 +2880,42 @@
         <v>5</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="6" t="s">
-        <v>55</v>
+      <c r="K14" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="N14" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="15" ht="85" customHeight="1" spans="1:14">
       <c r="A15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>17</v>
@@ -3244,42 +2924,42 @@
         <v>5</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="6" t="s">
-        <v>55</v>
+      <c r="K15" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="M15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="N15" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="16" ht="84" customHeight="1" spans="1:14">
       <c r="A16" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>17</v>
@@ -3288,42 +2968,42 @@
         <v>5</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="6" t="s">
-        <v>55</v>
+      <c r="K16" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="M16" s="2" t="s">
+      <c r="N16" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="17" ht="89" customHeight="1" spans="1:14">
       <c r="A17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>17</v>
@@ -3338,36 +3018,36 @@
         <v>29</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K17" s="6" t="s">
-        <v>55</v>
+      <c r="K17" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="M17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M17" s="2" t="s">
+      <c r="N17" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="18" ht="100" customHeight="1" spans="1:14">
       <c r="A18" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>17</v>
@@ -3382,36 +3062,36 @@
         <v>29</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="6" t="s">
-        <v>55</v>
+      <c r="K18" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M18" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="M18" s="2" t="s">
+      <c r="N18" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="19" ht="105" customHeight="1" spans="1:14">
       <c r="A19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>17</v>
@@ -3423,39 +3103,39 @@
         <v>29</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K19" s="6" t="s">
-        <v>55</v>
+      <c r="K19" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L19" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M19" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="M19" s="2" t="s">
+      <c r="N19" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="20" ht="110" customHeight="1" spans="1:14">
       <c r="A20" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>17</v>
@@ -3470,36 +3150,36 @@
         <v>29</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="6" t="s">
-        <v>55</v>
+      <c r="K20" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L20" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="M20" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="M20" s="2" t="s">
+      <c r="N20" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="21" ht="105" customHeight="1" spans="1:14">
       <c r="A21" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>17</v>
@@ -3511,39 +3191,39 @@
         <v>19</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K21" s="6" t="s">
-        <v>55</v>
+      <c r="K21" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L21" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M21" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="M21" s="2" t="s">
+      <c r="N21" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="22" ht="109" customHeight="1" spans="1:14">
       <c r="A22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>17</v>
@@ -3555,39 +3235,39 @@
         <v>18</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L22" s="2" t="s">
+      <c r="M22" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="M22" s="2" t="s">
+      <c r="N22" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="23" ht="104" customHeight="1" spans="1:14">
       <c r="A23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>17</v>
@@ -3599,86 +3279,86 @@
         <v>29</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H23" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="I23" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L23" s="2" t="s">
+      <c r="M23" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="M23" s="2" t="s">
+      <c r="N23" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="24" ht="103" customHeight="1" spans="1:14">
       <c r="A24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="E24" s="3">
         <v>8</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H24" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L24" s="2" t="s">
+      <c r="M24" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="M24" s="2" t="s">
+      <c r="N24" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="25" ht="120" customHeight="1" spans="1:14">
       <c r="A25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D25" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E25" s="3">
         <v>8</v>
@@ -3690,36 +3370,36 @@
         <v>29</v>
       </c>
       <c r="H25" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="I25" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L25" s="2" t="s">
+      <c r="M25" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="M25" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="26" ht="105" customHeight="1" spans="1:14">
       <c r="A26" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>17</v>
@@ -3734,83 +3414,83 @@
         <v>29</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L26" s="2" t="s">
+      <c r="M26" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="M26" s="2" t="s">
+      <c r="N26" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="27" ht="90" customHeight="1" spans="1:14">
       <c r="A27" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E27" s="3">
         <v>8</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>29</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L27" s="2" t="s">
+      <c r="M27" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="M27" s="2" t="s">
+      <c r="N27" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="28" ht="105" customHeight="1" spans="1:14">
       <c r="A28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E28" s="3">
         <v>8</v>
@@ -3822,36 +3502,36 @@
         <v>18</v>
       </c>
       <c r="H28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L28" s="2" t="s">
+      <c r="M28" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="M28" s="2" t="s">
+      <c r="N28" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="29" ht="86" customHeight="1" spans="1:14">
       <c r="A29" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>17</v>
@@ -3860,42 +3540,42 @@
         <v>5</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>18</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="J29" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="J29" s="3" t="s">
+      <c r="K29" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K29" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L29" s="2" t="s">
+      <c r="M29" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="N29" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="30" ht="86" customHeight="1" spans="1:14">
       <c r="A30" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>17</v>
@@ -3904,42 +3584,42 @@
         <v>8</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K30" s="6" t="s">
-        <v>55</v>
+      <c r="K30" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L30" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="M30" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="N30" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="31" ht="86" customHeight="1" spans="1:14">
       <c r="A31" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>206</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>17</v>
@@ -3948,42 +3628,42 @@
         <v>5</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K31" s="6" t="s">
-        <v>55</v>
+      <c r="K31" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L31" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="M31" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="N31" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="32" ht="105" customHeight="1" spans="1:14">
       <c r="A32" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>17</v>
@@ -3992,86 +3672,86 @@
         <v>13</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H32" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L32" s="2" t="s">
+      <c r="M32" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="N32" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="33" ht="75" customHeight="1" spans="1:14">
       <c r="A33" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E33" s="3">
         <v>8</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H33" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L33" s="2" t="s">
+      <c r="M33" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="M33" s="2" t="s">
+      <c r="N33" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="34" ht="85" customHeight="1" spans="1:14">
       <c r="A34" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>17</v>
@@ -4080,42 +3760,42 @@
         <v>8</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H34" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="J34" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L34" s="2" t="s">
+      <c r="M34" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="M34" s="2" t="s">
+      <c r="N34" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="35" ht="88" customHeight="1" spans="1:14">
       <c r="A35" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>17</v>
@@ -4124,42 +3804,42 @@
         <v>3</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K35" s="6" t="s">
-        <v>55</v>
+      <c r="K35" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L35" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="M35" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="M35" s="2" t="s">
+      <c r="N35" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="36" ht="88" customHeight="1" spans="1:14">
       <c r="A36" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>17</v>
@@ -4171,39 +3851,39 @@
         <v>19</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H36" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="J36" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="J36" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L36" s="2" t="s">
+      <c r="M36" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="M36" s="2" t="s">
+      <c r="N36" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="37" ht="90" customHeight="1" spans="1:14">
       <c r="A37" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>17</v>
@@ -4218,36 +3898,36 @@
         <v>18</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K37" s="6" t="s">
-        <v>55</v>
+      <c r="K37" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L37" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="M37" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="M37" s="2" t="s">
+      <c r="N37" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="38" ht="75" customHeight="1" spans="1:14">
       <c r="A38" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>17</v>
@@ -4262,36 +3942,36 @@
         <v>18</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="6" t="s">
-        <v>55</v>
+      <c r="K38" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L38" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="M38" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="M38" s="2" t="s">
+      <c r="N38" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="39" ht="75" customHeight="1" spans="1:14">
       <c r="A39" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>17</v>
@@ -4306,36 +3986,36 @@
         <v>18</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K39" s="6" t="s">
-        <v>55</v>
+      <c r="K39" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L39" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="M39" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="M39" s="2" t="s">
+      <c r="N39" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="40" ht="105" customHeight="1" spans="1:14">
       <c r="A40" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>17</v>
@@ -4350,36 +4030,36 @@
         <v>18</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K40" s="6" t="s">
-        <v>55</v>
+      <c r="K40" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L40" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="M40" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M40" s="2" t="s">
+      <c r="N40" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="41" ht="90" customHeight="1" spans="1:14">
       <c r="A41" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>17</v>
@@ -4394,36 +4074,36 @@
         <v>18</v>
       </c>
       <c r="H41" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="I41" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K41" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L41" s="2" t="s">
+      <c r="M41" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="M41" s="2" t="s">
+      <c r="N41" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="42" ht="75" customHeight="1" spans="1:14">
       <c r="A42" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>17</v>
@@ -4435,42 +4115,42 @@
         <v>29</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H42" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="I42" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L42" s="2" t="s">
+      <c r="M42" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="M42" s="2" t="s">
+      <c r="N42" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="43" ht="85" customHeight="1" spans="1:14">
       <c r="A43" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E43" s="3">
         <v>5</v>
@@ -4482,36 +4162,36 @@
         <v>18</v>
       </c>
       <c r="H43" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="I43" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K43" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L43" s="2" t="s">
+      <c r="M43" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="M43" s="2" t="s">
+      <c r="N43" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="44" ht="105" customHeight="1" spans="1:14">
       <c r="A44" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>17</v>
@@ -4526,39 +4206,39 @@
         <v>18</v>
       </c>
       <c r="H44" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K44" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L44" s="2" t="s">
+      <c r="M44" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="M44" s="2" t="s">
+      <c r="N44" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="45" ht="84" customHeight="1" spans="1:14">
       <c r="A45" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>293</v>
-      </c>
       <c r="D45" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E45" s="3">
         <v>5</v>
@@ -4570,36 +4250,36 @@
         <v>18</v>
       </c>
       <c r="H45" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K45" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L45" s="2" t="s">
+      <c r="M45" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="M45" s="2" t="s">
+      <c r="N45" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="46" ht="88" customHeight="1" spans="1:14">
       <c r="A46" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>17</v>
@@ -4614,36 +4294,36 @@
         <v>19</v>
       </c>
       <c r="H46" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="I46" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="I46" s="2" t="s">
+      <c r="J46" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K46" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L46" s="2" t="s">
+      <c r="M46" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="M46" s="2" t="s">
+      <c r="N46" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="47" ht="85" customHeight="1" spans="1:14">
       <c r="A47" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>17</v>
@@ -4652,42 +4332,42 @@
         <v>8</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H47" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K47" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L47" s="2" t="s">
+      <c r="M47" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="M47" s="2" t="s">
+      <c r="N47" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="48" ht="105" customHeight="1" spans="1:14">
       <c r="A48" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>17</v>
@@ -4696,42 +4376,42 @@
         <v>8</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>19</v>
       </c>
       <c r="H48" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="I48" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L48" s="2" t="s">
+      <c r="M48" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="M48" s="2" t="s">
+      <c r="N48" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="49" ht="90" customHeight="1" spans="1:14">
       <c r="A49" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>17</v>
@@ -4743,42 +4423,42 @@
         <v>19</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H49" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="I49" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K49" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L49" s="2" t="s">
+      <c r="M49" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="N49" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="50" ht="90" customHeight="1" spans="1:14">
       <c r="A50" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="D50" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="E50" s="3">
         <v>8</v>
@@ -4790,36 +4470,36 @@
         <v>18</v>
       </c>
       <c r="H50" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K50" s="6" t="s">
+      <c r="M50" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="L50" s="2" t="s">
+      <c r="N50" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="51" ht="85" customHeight="1" spans="1:14">
       <c r="A51" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>17</v>
@@ -4834,36 +4514,36 @@
         <v>18</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K51" s="6" t="s">
-        <v>55</v>
+      <c r="K51" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="L51" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="N51" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="52" ht="75" customHeight="1" spans="1:14">
       <c r="A52" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>17</v>
@@ -4878,36 +4558,36 @@
         <v>18</v>
       </c>
       <c r="H52" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="M52" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K52" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L52" s="2" t="s">
+      <c r="N52" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="M52" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="N52" s="2" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="53" ht="84" customHeight="1" spans="1:14">
       <c r="A53" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>17</v>
@@ -4922,36 +4602,36 @@
         <v>18</v>
       </c>
       <c r="H53" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="I53" s="2" t="s">
+      <c r="M53" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="J53" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K53" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L53" s="2" t="s">
+      <c r="N53" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="54" ht="89" customHeight="1" spans="1:14">
       <c r="A54" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>17</v>
@@ -4966,36 +4646,36 @@
         <v>29</v>
       </c>
       <c r="H54" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="I54" s="2" t="s">
+      <c r="M54" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K54" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L54" s="2" t="s">
+      <c r="N54" s="2" t="s">
         <v>357</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="N54" s="2" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="55" ht="87" customHeight="1" spans="1:14">
       <c r="A55" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>17</v>
@@ -5010,36 +4690,36 @@
         <v>29</v>
       </c>
       <c r="H55" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="I55" s="2" t="s">
+      <c r="M55" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="J55" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K55" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L55" s="2" t="s">
+      <c r="N55" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="M55" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="56" ht="85" customHeight="1" spans="1:14">
       <c r="A56" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>17</v>
@@ -5054,36 +4734,36 @@
         <v>18</v>
       </c>
       <c r="H56" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="I56" s="2" t="s">
+      <c r="M56" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="J56" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L56" s="2" t="s">
+      <c r="N56" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="M56" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="57" ht="105" customHeight="1" spans="1:14">
       <c r="A57" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>376</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>17</v>
@@ -5098,36 +4778,36 @@
         <v>19</v>
       </c>
       <c r="H57" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="M57" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="I57" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K57" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L57" s="2" t="s">
+      <c r="N57" s="2" t="s">
         <v>378</v>
-      </c>
-      <c r="M57" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="N57" s="2" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="58" ht="85" customHeight="1" spans="1:14">
       <c r="A58" s="3" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>17</v>
@@ -5142,36 +4822,36 @@
         <v>19</v>
       </c>
       <c r="H58" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="M58" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="I58" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K58" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L58" s="2" t="s">
+      <c r="N58" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="M58" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="N58" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="59" ht="99" customHeight="1" spans="1:14">
       <c r="A59" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>17</v>
@@ -5186,25 +4866,25 @@
         <v>19</v>
       </c>
       <c r="H59" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="M59" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="I59" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="K59" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L59" s="2" t="s">
+      <c r="N59" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="N59" s="2" t="s">
-        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -5233,33 +4913,33 @@
   <sheetData>
     <row r="1" ht="71" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B2" s="3">
         <v>18</v>
@@ -5268,7 +4948,7 @@
         <v>96</v>
       </c>
       <c r="D2" s="3">
-        <v>24.7</v>
+        <v>24.2</v>
       </c>
       <c r="E2" s="3">
         <v>39</v>
@@ -5277,15 +4957,15 @@
         <v>57</v>
       </c>
       <c r="G2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="3">
-        <v>119</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:8">
       <c r="A3" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B3" s="3">
         <v>13</v>
@@ -5294,7 +4974,7 @@
         <v>99</v>
       </c>
       <c r="D3" s="3">
-        <v>25.4</v>
+        <v>24.9</v>
       </c>
       <c r="E3" s="3">
         <v>39</v>
@@ -5311,22 +4991,22 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:8">
       <c r="A4" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B4" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D4" s="3">
-        <v>24.9</v>
+        <v>26.5</v>
       </c>
       <c r="E4" s="3">
         <v>37</v>
       </c>
       <c r="F4" s="3">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G4" s="3">
         <v>21</v>
@@ -5337,7 +5017,7 @@
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:8">
       <c r="A5" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B5" s="3">
         <v>14</v>
@@ -5346,7 +5026,7 @@
         <v>97</v>
       </c>
       <c r="D5" s="3">
-        <v>24.9</v>
+        <v>24.4</v>
       </c>
       <c r="E5" s="3">
         <v>36</v>
@@ -5363,13 +5043,13 @@
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="B6" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="3">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="D6" s="3">
         <v>100</v>
@@ -5378,13 +5058,13 @@
         <v>151</v>
       </c>
       <c r="F6" s="3">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="G6" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H6" s="3">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
   </sheetData>
